--- a/AAII_Financials/Quarterly/BUD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BUD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="92">
   <si>
     <t>BUD</t>
   </si>
@@ -656,517 +656,529 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>16660000</v>
+      </c>
+      <c r="E8" s="3">
         <v>15556000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>15004000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>14841000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>15333000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>14473000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>15120000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>14668000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>14792000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>15574000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>15120000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>14213000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>14668000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>15091000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>14792000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>13235000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>14198000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>14274000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>13539000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>12293000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>12767000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>12816000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>21298000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>11003000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>13335000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>13172000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>13599000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>12224000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>13792000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>12916000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>27087000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>13095000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>29340000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>14740000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>27104000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>12922000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>25311000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>11109000</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7082000</v>
+      </c>
+      <c r="E9" s="3">
         <v>6943000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6558000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6644000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6766000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6679000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>7019000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6661000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6795000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>7180000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>7019000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6517000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6661000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6860000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6795000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>5989000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>6096000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>6039000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>5720000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>5243000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>5282000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>5255000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>9097000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4573000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>5270000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>5140000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>5176000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4777000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>5064000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>4861000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>10165000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>5002000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>10712000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>5546000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>10674000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>5229000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>9801000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>4393000</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>9578000</v>
+      </c>
+      <c r="E10" s="3">
         <v>8613000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>8446000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>8197000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>8567000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>7794000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>8101000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>8007000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>7997000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>8394000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>8101000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>7696000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>8007000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>8231000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>7997000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>7246000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>8102000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>8235000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>7819000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>7050000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>7485000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>7561000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>12201000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>6430000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>8065000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>8032000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>8423000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>7447000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>8728000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>8055000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>16922000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>8093000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>18628000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>9194000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>16430000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>7693000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>15510000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>6716000</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1207,35 +1219,36 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3">
         <v>194000</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="3">
+      <c r="F12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="3">
         <v>222000</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="3">
         <v>256000</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="J12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="3">
         <v>268000</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1323,8 +1336,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1439,163 +1455,169 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-1360000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-197000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>300000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>211000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>207000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-651000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1073000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-1636000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-328000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>268000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1073000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-329000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-363000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>165000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>9000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>223000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>198000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>542000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>403000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>393000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-206000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>564000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>3475000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>44000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1135000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-261000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-12000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>45000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>724000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>52000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>1184000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>426000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>780000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>218000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>287000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>221000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>411000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>914500</v>
+      </c>
+      <c r="E15" s="3">
         <v>934500</v>
       </c>
-      <c r="E15" s="3">
-        <v>904500</v>
-      </c>
       <c r="F15" s="3">
+        <v>1290500</v>
+      </c>
+      <c r="G15" s="3">
         <v>1124500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1370500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1093300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1297500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1068300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1238500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>948800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1297500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>948800</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1671,8 +1693,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1710,240 +1735,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>12105000</v>
+      </c>
+      <c r="E17" s="3">
         <v>11675000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>11010000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>11116000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>11451000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>11126000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>11572000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>11361000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11001000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>11568000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>11572000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>10730000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>10697000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>11201000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>10990000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>10164000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>10747000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>10796000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>10288000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>9573000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>8694000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>9626000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>19671000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>8242000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>10342000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>8797000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>9190000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>8602000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>9663000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>8793000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>19292000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>9561000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>20367000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>10277000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>19331000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>9421000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>18360000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>8078000</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4555000</v>
+      </c>
+      <c r="E18" s="3">
         <v>3881000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3994000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3725000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3882000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3347000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3548000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3307000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3791000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4006000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3548000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3483000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3971000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3890000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3802000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3071000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3451000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3478000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3251000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2720000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>4073000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3190000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1627000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2761000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2993000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>4375000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>4409000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3622000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>4129000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>4123000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>7795000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3534000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>8973000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>4463000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>7773000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>3501000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>6951000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>3031000</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1984,163 +2016,167 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>251000</v>
+      </c>
+      <c r="E20" s="3">
         <v>113000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>227000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>71000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>374000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>323000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>403000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>501000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>573000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>346000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>403000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>392000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-679000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1376000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1106000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2049000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-666000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2105000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-367000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1299000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-636000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1295000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-4880000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-4708000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2180000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-381000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-870000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>809000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-2767000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-2360000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-676000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-1520000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-342000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-825000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-1036000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-1339000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-2004000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-1856000</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5218500</v>
+      </c>
+      <c r="E21" s="3">
         <v>4702500</v>
       </c>
-      <c r="E21" s="3">
-        <v>4671500</v>
-      </c>
       <c r="F21" s="3">
+        <v>5057500</v>
+      </c>
+      <c r="G21" s="3">
         <v>4778500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4878500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4117300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4442500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3874300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4456500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4608800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4442500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4039800</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
@@ -2192,71 +2228,74 @@
       <c r="AF21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH21" s="3">
         <v>9454000</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI21" s="3">
+      <c r="AI21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>10798000</v>
       </c>
-      <c r="AJ21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK21" s="3">
+      <c r="AK21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL21" s="3">
         <v>8846000</v>
       </c>
-      <c r="AL21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM21" s="3">
+      <c r="AM21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN21" s="3">
         <v>6865000</v>
       </c>
-      <c r="AN21" s="3" t="s">
+      <c r="AO21" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1007000</v>
+      </c>
+      <c r="E22" s="3">
         <v>1379000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1006000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1400000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1115000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1487000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1142000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1298000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1000000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>789000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1142000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>806000</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
       <c r="P22" s="3">
         <v>0</v>
       </c>
@@ -2296,8 +2335,8 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>8</v>
+      <c r="AC22" s="3">
+        <v>0</v>
       </c>
       <c r="AD22" s="3" t="s">
         <v>8</v>
@@ -2308,264 +2347,273 @@
       <c r="AF22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AG22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH22" s="3">
         <v>2109000</v>
       </c>
-      <c r="AH22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI22" s="3">
+      <c r="AI22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>2121000</v>
       </c>
-      <c r="AJ22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK22" s="3">
+      <c r="AK22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL22" s="3">
         <v>2171000</v>
       </c>
-      <c r="AL22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM22" s="3">
+      <c r="AM22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN22" s="3">
         <v>2277000</v>
       </c>
-      <c r="AN22" s="3" t="s">
+      <c r="AO22" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5002000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3097000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2764000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2539000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2504000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2646000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1202000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3292000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2695000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2632000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1202000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2645000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3292000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2514000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2696000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1022000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2785000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1373000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2884000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1421000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3437000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1895000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3253000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1947000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>813000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>3994000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>3539000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>4431000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1362000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1763000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>5010000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2014000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>6510000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>3638000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>4566000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>2162000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>2670000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>1175000</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>918000</v>
+      </c>
+      <c r="E24" s="3">
         <v>720000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>740000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>848000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>752000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>376000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>595000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-5000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>720000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>666000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>595000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>597000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-5000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>688000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>720000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>524000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>440000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>679000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>702000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>529000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>830000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>610000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>492000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>318000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>454000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>768000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>894000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>671000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>679000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>605000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1420000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>666000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>927800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>1494000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>994000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>418000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>778000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>225000</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2680,240 +2728,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4084000</v>
+      </c>
+      <c r="E26" s="3">
         <v>2377000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2024000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1691000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1752000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2270000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>607000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3297000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1975000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1966000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>607000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2048000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3297000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1826000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1976000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>498000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2345000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>694000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2182000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>892000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2607000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1285000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3745000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-2265000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>359000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>3226000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2645000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3760000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>683000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1158000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>3590000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1348000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>5582200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>2144000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>3572000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1744000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>1892000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>950000</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3751000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1959000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1676000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1220000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1473000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1891000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>338000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2843000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1597000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1472000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>338000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1639000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2843000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1433000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1597000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>95000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1961000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>250000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1863000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>595000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2265000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1039000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3952000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-2375000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2930000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2369000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3450000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>300000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>862000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2954000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1019000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>5086200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>2055000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>2880000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>1377000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>908000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>557000</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3028,8 +3085,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3081,11 +3141,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V29" s="3">
         <v>0</v>
@@ -3097,55 +3157,58 @@
         <v>0</v>
       </c>
       <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>2055000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>125000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>114000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>73000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>115000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>121000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>157000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>99000</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
       <c r="AH29" s="3">
         <v>0</v>
       </c>
       <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>1800</v>
       </c>
-      <c r="AJ29" s="3">
-        <v>0</v>
-      </c>
       <c r="AK29" s="3">
-        <v>28000</v>
+        <v>0</v>
       </c>
       <c r="AL29" s="3">
         <v>28000</v>
       </c>
       <c r="AM29" s="3">
+        <v>28000</v>
+      </c>
+      <c r="AN29" s="3">
         <v>48000</v>
       </c>
-      <c r="AN29" s="3" t="s">
+      <c r="AO29" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3260,8 +3323,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3376,240 +3442,249 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-251000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-113000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-227000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-71000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-374000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-323000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-403000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-501000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-573000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-346000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-403000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-392000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>679000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1376000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1106000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2049000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>666000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2105000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>367000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1299000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>636000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1295000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>4880000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>4708000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2180000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>381000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>870000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-809000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>2767000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>2360000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>676000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>1520000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>342000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>825000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>1036000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>1339000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>2004000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>1856000</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3751000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1959000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1676000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1220000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1473000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1891000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>338000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2843000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1597000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1472000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>338000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1639000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2843000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1433000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1597000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>95000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1961000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>250000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1863000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>595000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2265000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1039000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1897000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2250000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>113000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>3003000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2484000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3571000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>457000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>961000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2954000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1019000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>5088000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>2055000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>2908000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>1405000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>956000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>557000</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3724,245 +3799,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3751000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1959000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1676000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1220000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1473000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1891000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>338000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2843000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1597000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1472000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>338000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1639000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2843000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1433000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1597000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>95000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1961000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>250000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1863000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>595000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2265000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1039000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1897000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2250000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>113000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>3003000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2484000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3571000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>457000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>961000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2954000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1019000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>5088000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>2055000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>2908000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>1405000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>956000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>557000</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4003,8 +4087,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4045,44 +4130,45 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7658000</v>
+      </c>
+      <c r="E41" s="3">
         <v>11638000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7167000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>11174000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7392000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>10332000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6848000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9973000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7027000</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M41" s="3">
+      <c r="M41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N41" s="3">
         <v>6848000</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>8</v>
       </c>
@@ -4119,88 +4205,91 @@
       <c r="Z41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AA41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB41" s="3">
         <v>5002000</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC41" s="3">
+      <c r="AC41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD41" s="3">
         <v>4896000</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE41" s="3">
+      <c r="AE41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF41" s="3">
         <v>4841000</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG41" s="3">
+      <c r="AG41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH41" s="3">
         <v>4651000</v>
       </c>
-      <c r="AH41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI41" s="3">
+      <c r="AI41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ41" s="3">
         <v>6576000</v>
       </c>
-      <c r="AJ41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK41" s="3">
+      <c r="AK41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL41" s="3">
         <v>4447000</v>
       </c>
-      <c r="AL41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM41" s="3">
+      <c r="AM41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN41" s="3">
         <v>10696000</v>
       </c>
-      <c r="AN41" s="3" t="s">
+      <c r="AO41" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>353000</v>
+      </c>
+      <c r="E42" s="3">
         <v>306000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>205000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>221000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>252000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>67000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>85000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>97000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>334000</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>85000</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>8</v>
+      <c r="O42" s="3">
+        <v>0</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>8</v>
@@ -4235,86 +4324,89 @@
       <c r="Z42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AA42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB42" s="3">
         <v>2328000</v>
       </c>
-      <c r="AB42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC42" s="3">
+      <c r="AC42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD42" s="3">
         <v>3370000</v>
       </c>
-      <c r="AD42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE42" s="3">
+      <c r="AE42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF42" s="3">
         <v>2320000</v>
       </c>
-      <c r="AF42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG42" s="3">
+      <c r="AG42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH42" s="3">
         <v>3323000</v>
       </c>
-      <c r="AH42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI42" s="3">
+      <c r="AI42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ42" s="3">
         <v>5200000</v>
       </c>
-      <c r="AJ42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK42" s="3">
+      <c r="AK42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL42" s="3">
         <v>5875000</v>
       </c>
-      <c r="AL42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM42" s="3">
+      <c r="AM42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN42" s="3">
         <v>17780000</v>
       </c>
-      <c r="AN42" s="3" t="s">
+      <c r="AO42" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7256000</v>
+      </c>
+      <c r="E43" s="3">
         <v>6378000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>7079000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5504000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6682000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6372000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7004000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5733000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5834000</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N43" s="3">
         <v>7004000</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>8</v>
       </c>
@@ -4351,86 +4443,89 @@
       <c r="Z43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AA43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB43" s="3">
         <v>6814000</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC43" s="3">
+      <c r="AC43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD43" s="3">
         <v>6850000</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE43" s="3">
+      <c r="AE43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF43" s="3">
         <v>6832000</v>
       </c>
-      <c r="AF43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG43" s="3">
+      <c r="AG43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH43" s="3">
         <v>7585000</v>
       </c>
-      <c r="AH43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI43" s="3">
+      <c r="AI43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ43" s="3">
         <v>7474000</v>
       </c>
-      <c r="AJ43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK43" s="3">
+      <c r="AK43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL43" s="3">
         <v>8036000</v>
       </c>
-      <c r="AL43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM43" s="3">
+      <c r="AM43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN43" s="3">
         <v>14967000</v>
       </c>
-      <c r="AN43" s="3" t="s">
+      <c r="AO43" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5528000</v>
+      </c>
+      <c r="E44" s="3">
         <v>5107000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5475000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5020000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5567000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5583000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6839000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>6612000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>6107000</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N44" s="3">
         <v>6839000</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>8</v>
       </c>
@@ -4467,86 +4562,89 @@
       <c r="Z44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AA44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB44" s="3">
         <v>4427000</v>
       </c>
-      <c r="AB44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC44" s="3">
+      <c r="AC44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD44" s="3">
         <v>4658000</v>
       </c>
-      <c r="AD44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE44" s="3">
+      <c r="AE44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF44" s="3">
         <v>4234000</v>
       </c>
-      <c r="AF44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG44" s="3">
+      <c r="AG44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH44" s="3">
         <v>4200000</v>
       </c>
-      <c r="AH44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI44" s="3">
+      <c r="AI44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ44" s="3">
         <v>4119000</v>
       </c>
-      <c r="AJ44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK44" s="3">
+      <c r="AK44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL44" s="3">
         <v>4279000</v>
       </c>
-      <c r="AL44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM44" s="3">
+      <c r="AM44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN44" s="3">
         <v>7802000</v>
       </c>
-      <c r="AN44" s="3" t="s">
+      <c r="AO44" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>677000</v>
+      </c>
+      <c r="E45" s="3">
         <v>773000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>502000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>587000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>499000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>539000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>190000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>361000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>879000</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3">
         <v>190000</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4583,86 +4681,89 @@
       <c r="Z45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AA45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB45" s="3">
         <v>10243000</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC45" s="3">
+      <c r="AC45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD45" s="3">
         <v>282000</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE45" s="3">
+      <c r="AE45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF45" s="3">
         <v>54000</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG45" s="3">
+      <c r="AG45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH45" s="3">
         <v>684000</v>
       </c>
-      <c r="AH45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI45" s="3">
+      <c r="AI45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ45" s="3">
         <v>591000</v>
       </c>
-      <c r="AJ45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK45" s="3">
+      <c r="AK45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL45" s="3">
         <v>7844000</v>
       </c>
-      <c r="AL45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM45" s="3">
+      <c r="AM45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN45" s="3">
         <v>34833000</v>
       </c>
-      <c r="AN45" s="3" t="s">
+      <c r="AO45" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>22242000</v>
+      </c>
+      <c r="E46" s="3">
         <v>24770000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>21215000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>22999000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>21026000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>23367000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>21483000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>23186000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>20720000</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M46" s="3">
+      <c r="M46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N46" s="3">
         <v>21483000</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>8</v>
       </c>
@@ -4699,86 +4800,89 @@
       <c r="Z46" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AA46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB46" s="3">
         <v>28814000</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC46" s="3">
+      <c r="AC46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD46" s="3">
         <v>20056000</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE46" s="3">
+      <c r="AE46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF46" s="3">
         <v>18281000</v>
       </c>
-      <c r="AF46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG46" s="3">
+      <c r="AG46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH46" s="3">
         <v>20443000</v>
       </c>
-      <c r="AH46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI46" s="3">
+      <c r="AI46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ46" s="3">
         <v>23960000</v>
       </c>
-      <c r="AJ46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK46" s="3">
+      <c r="AK46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL46" s="3">
         <v>30481000</v>
       </c>
-      <c r="AL46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM46" s="3">
+      <c r="AM46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN46" s="3">
         <v>43017000</v>
       </c>
-      <c r="AN46" s="3" t="s">
+      <c r="AO46" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>5227000</v>
+      </c>
+      <c r="E47" s="3">
         <v>5163000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>5030000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>4780000</v>
-      </c>
-      <c r="G47" s="3">
-        <v>5050000</v>
       </c>
       <c r="H47" s="3">
         <v>5050000</v>
       </c>
       <c r="I47" s="3">
+        <v>5050000</v>
+      </c>
+      <c r="J47" s="3">
         <v>4907000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>4831000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4697000</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N47" s="3">
         <v>4907000</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
@@ -4815,86 +4919,89 @@
       <c r="Z47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AA47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB47" s="3">
         <v>7859000</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC47" s="3">
+      <c r="AC47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD47" s="3">
         <v>7884000</v>
       </c>
-      <c r="AD47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE47" s="3">
+      <c r="AE47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF47" s="3">
         <v>8005000</v>
       </c>
-      <c r="AF47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG47" s="3">
+      <c r="AG47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH47" s="3">
         <v>7711000</v>
       </c>
-      <c r="AH47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI47" s="3">
+      <c r="AI47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ47" s="3">
         <v>6905000</v>
       </c>
-      <c r="AJ47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK47" s="3">
+      <c r="AK47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL47" s="3">
         <v>7326000</v>
       </c>
-      <c r="AL47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM47" s="3">
+      <c r="AM47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN47" s="3">
         <v>10560000</v>
       </c>
-      <c r="AN47" s="3" t="s">
+      <c r="AO47" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>22998000</v>
+      </c>
+      <c r="E48" s="3">
         <v>23664000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>23854000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>23503000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>25086000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>26818000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>27181000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>26671000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>26320000</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N48" s="3">
         <v>27181000</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>8</v>
       </c>
@@ -4931,88 +5038,91 @@
       <c r="Z48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AA48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB48" s="3">
         <v>27544000</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC48" s="3">
+      <c r="AC48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD48" s="3">
         <v>27517000</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE48" s="3">
+      <c r="AE48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF48" s="3">
         <v>27615000</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG48" s="3">
+      <c r="AG48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH48" s="3">
         <v>25451000</v>
       </c>
-      <c r="AH48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI48" s="3">
+      <c r="AI48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ48" s="3">
         <v>27184000</v>
       </c>
-      <c r="AJ48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK48" s="3">
+      <c r="AK48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL48" s="3">
         <v>26372000</v>
       </c>
-      <c r="AL48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM48" s="3">
+      <c r="AM48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN48" s="3">
         <v>53741000</v>
       </c>
-      <c r="AN48" s="3" t="s">
+      <c r="AO48" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>162220000</v>
+      </c>
+      <c r="E49" s="3">
         <v>159893000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>155878000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>150513000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>154154000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>158329000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>157141000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>153219000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>155813000</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
       <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
         <v>157141000</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
-      <c r="O49" s="3" t="s">
-        <v>8</v>
+      <c r="O49" s="3">
+        <v>0</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>8</v>
@@ -5047,50 +5157,53 @@
       <c r="Z49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AA49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB49" s="3">
         <v>170566000</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC49" s="3">
+      <c r="AC49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD49" s="3">
         <v>179947000</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE49" s="3">
+      <c r="AE49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF49" s="3">
         <v>178142000</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG49" s="3">
+      <c r="AG49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH49" s="3">
         <v>182144000</v>
       </c>
-      <c r="AH49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI49" s="3">
+      <c r="AI49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ49" s="3">
         <v>186814000</v>
       </c>
-      <c r="AJ49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK49" s="3">
+      <c r="AK49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL49" s="3">
         <v>187607000</v>
       </c>
-      <c r="AL49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM49" s="3">
+      <c r="AM49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN49" s="3">
         <v>361754000</v>
       </c>
-      <c r="AN49" s="3" t="s">
+      <c r="AO49" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5205,8 +5318,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5321,44 +5437,47 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2581000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2281000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2141000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2129000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2444000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2559000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2495000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2428000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2280000</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N52" s="3">
         <v>2495000</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>8</v>
       </c>
@@ -5395,50 +5514,53 @@
       <c r="Z52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AA52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB52" s="3">
         <v>1865000</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC52" s="3">
+      <c r="AC52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD52" s="3">
         <v>1931000</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE52" s="3">
+      <c r="AE52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF52" s="3">
         <v>1825000</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG52" s="3">
+      <c r="AG52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH52" s="3">
         <v>1648000</v>
       </c>
-      <c r="AH52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI52" s="3">
+      <c r="AI52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>1263000</v>
       </c>
-      <c r="AJ52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK52" s="3">
+      <c r="AK52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL52" s="3">
         <v>151000</v>
       </c>
-      <c r="AL52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM52" s="3">
+      <c r="AM52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN52" s="3">
         <v>2834000</v>
       </c>
-      <c r="AN52" s="3" t="s">
+      <c r="AO52" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5553,44 +5675,47 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>218385000</v>
+      </c>
+      <c r="E54" s="3">
         <v>218808000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>211107000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>206637000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>210720000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>219340000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>216352000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>212943000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>212397000</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M54" s="3">
+      <c r="M54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N54" s="3">
         <v>216352000</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>8</v>
       </c>
@@ -5627,50 +5752,53 @@
       <c r="Z54" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AA54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB54" s="3">
         <v>236648000</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC54" s="3">
+      <c r="AC54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD54" s="3">
         <v>237335000</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE54" s="3">
+      <c r="AE54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF54" s="3">
         <v>233868000</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG54" s="3">
+      <c r="AG54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH54" s="3">
         <v>237397000</v>
       </c>
-      <c r="AH54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI54" s="3">
+      <c r="AI54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ54" s="3">
         <v>246126000</v>
       </c>
-      <c r="AJ54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK54" s="3">
+      <c r="AK54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL54" s="3">
         <v>251937000</v>
       </c>
-      <c r="AL54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM54" s="3">
+      <c r="AM54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN54" s="3">
         <v>256586000</v>
       </c>
-      <c r="AN54" s="3" t="s">
+      <c r="AO54" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5711,8 +5839,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5753,44 +5882,45 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>24605000</v>
+      </c>
+      <c r="E57" s="3">
         <v>17054000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>22188000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>16010000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>21708000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>17729000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>23347000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>18589000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>22748000</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N57" s="3">
         <v>23347000</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>8</v>
       </c>
@@ -5827,88 +5957,91 @@
       <c r="Z57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AA57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB57" s="3">
         <v>15876000</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC57" s="3">
+      <c r="AC57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD57" s="3">
         <v>14538000</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE57" s="3">
+      <c r="AE57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF57" s="3">
         <v>15512000</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG57" s="3">
+      <c r="AG57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH57" s="3">
         <v>13647000</v>
       </c>
-      <c r="AH57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI57" s="3">
+      <c r="AI57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ57" s="3">
         <v>15240000</v>
       </c>
-      <c r="AJ57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK57" s="3">
+      <c r="AK57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL57" s="3">
         <v>13075000</v>
       </c>
-      <c r="AL57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM57" s="3">
+      <c r="AM57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN57" s="3">
         <v>28142000</v>
       </c>
-      <c r="AN57" s="3" t="s">
+      <c r="AO57" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3594000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1061000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3684000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1533000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2312000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4028000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2730000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1304000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1414000</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>2730000</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>8</v>
+      <c r="O58" s="3">
+        <v>0</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>8</v>
@@ -5943,86 +6076,89 @@
       <c r="Z58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AA58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB58" s="3">
         <v>5478000</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC58" s="3">
+      <c r="AC58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD58" s="3">
         <v>11069000</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE58" s="3">
+      <c r="AE58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF58" s="3">
         <v>4698000</v>
       </c>
-      <c r="AF58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG58" s="3">
+      <c r="AG58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH58" s="3">
         <v>6046000</v>
       </c>
-      <c r="AH58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI58" s="3">
+      <c r="AI58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ58" s="3">
         <v>7550000</v>
       </c>
-      <c r="AJ58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK58" s="3">
+      <c r="AK58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL58" s="3">
         <v>11484000</v>
       </c>
-      <c r="AL58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM58" s="3">
+      <c r="AM58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN58" s="3">
         <v>17604000</v>
       </c>
-      <c r="AN58" s="3" t="s">
+      <c r="AO58" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5277000</v>
+      </c>
+      <c r="E59" s="3">
         <v>9271000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7137000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8987000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6546000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8363000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7696000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7762000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6730000</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N59" s="3">
         <v>7696000</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>8</v>
       </c>
@@ -6059,86 +6195,89 @@
       <c r="Z59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AA59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB59" s="3">
         <v>13487000</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC59" s="3">
+      <c r="AC59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD59" s="3">
         <v>11669000</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE59" s="3">
+      <c r="AE59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF59" s="3">
         <v>14617000</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG59" s="3">
+      <c r="AG59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH59" s="3">
         <v>10960000</v>
       </c>
-      <c r="AH59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI59" s="3">
+      <c r="AI59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ59" s="3">
         <v>13421000</v>
       </c>
-      <c r="AJ59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK59" s="3">
+      <c r="AK59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL59" s="3">
         <v>12427000</v>
       </c>
-      <c r="AL59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM59" s="3">
+      <c r="AM59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN59" s="3">
         <v>34739000</v>
       </c>
-      <c r="AN59" s="3" t="s">
+      <c r="AO59" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>33476000</v>
+      </c>
+      <c r="E60" s="3">
         <v>34475000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>33009000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>33066000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>30566000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>37156000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>33773000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>34383000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>30892000</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M60" s="3">
+      <c r="M60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N60" s="3">
         <v>33773000</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>8</v>
       </c>
@@ -6175,86 +6314,89 @@
       <c r="Z60" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AA60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB60" s="3">
         <v>34841000</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC60" s="3">
+      <c r="AC60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD60" s="3">
         <v>37276000</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE60" s="3">
+      <c r="AE60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF60" s="3">
         <v>34826000</v>
       </c>
-      <c r="AF60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG60" s="3">
+      <c r="AG60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH60" s="3">
         <v>30653000</v>
       </c>
-      <c r="AH60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI60" s="3">
+      <c r="AI60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ60" s="3">
         <v>36211000</v>
       </c>
-      <c r="AJ60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK60" s="3">
+      <c r="AK60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL60" s="3">
         <v>36986000</v>
       </c>
-      <c r="AL60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM60" s="3">
+      <c r="AM60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN60" s="3">
         <v>40369000</v>
       </c>
-      <c r="AN60" s="3" t="s">
+      <c r="AO60" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>69138000</v>
+      </c>
+      <c r="E61" s="3">
         <v>72273000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>72153000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>70787000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>75944000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>74313000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>78323000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>78880000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>82117000</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>78323000</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -6292,85 +6434,88 @@
         <v>0</v>
       </c>
       <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
         <v>97564000</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
         <v>101672000</v>
       </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
       <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
         <v>106997000</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
       <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
         <v>110949000</v>
       </c>
-      <c r="AH61" s="3">
-        <v>0</v>
-      </c>
       <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ61" s="3">
         <v>108949000</v>
       </c>
-      <c r="AJ61" s="3">
-        <v>0</v>
-      </c>
       <c r="AK61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL61" s="3">
         <v>108281000</v>
       </c>
-      <c r="AL61" s="3">
-        <v>0</v>
-      </c>
       <c r="AM61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN61" s="3">
         <v>113941000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1759000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1649000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1859000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1467000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1712000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1648000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1948000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2050000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2430000</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N62" s="3">
         <v>1948000</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>8</v>
       </c>
@@ -6407,50 +6552,53 @@
       <c r="Z62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AA62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB62" s="3">
         <v>19690000</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC62" s="3">
+      <c r="AC62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD62" s="3">
         <v>20256000</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE62" s="3">
+      <c r="AE62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF62" s="3">
         <v>20156000</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG62" s="3">
+      <c r="AG62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH62" s="3">
         <v>20231000</v>
       </c>
-      <c r="AH62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI62" s="3">
+      <c r="AI62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ62" s="3">
         <v>20746000</v>
       </c>
-      <c r="AJ62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK62" s="3">
+      <c r="AK62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL62" s="3">
         <v>23191000</v>
       </c>
-      <c r="AL62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM62" s="3">
+      <c r="AM62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN62" s="3">
         <v>43750000</v>
       </c>
-      <c r="AN62" s="3" t="s">
+      <c r="AO62" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6565,8 +6713,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6681,8 +6832,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6797,44 +6951,47 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>117200000</v>
+      </c>
+      <c r="E66" s="3">
         <v>121072000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>119693000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>117937000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>121478000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>126664000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>127568000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>128665000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>129647000</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M66" s="3">
+      <c r="M66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N66" s="3">
         <v>127568000</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>8</v>
       </c>
@@ -6871,50 +7028,53 @@
       <c r="Z66" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AA66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB66" s="3">
         <v>160926000</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC66" s="3">
+      <c r="AC66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD66" s="3">
         <v>167102000</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE66" s="3">
+      <c r="AE66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF66" s="3">
         <v>169383000</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG66" s="3">
+      <c r="AG66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH66" s="3">
         <v>168887000</v>
       </c>
-      <c r="AH66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI66" s="3">
+      <c r="AI66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ66" s="3">
         <v>173541000</v>
       </c>
-      <c r="AJ66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK66" s="3">
+      <c r="AK66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL66" s="3">
         <v>179223000</v>
       </c>
-      <c r="AL66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM66" s="3">
+      <c r="AM66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN66" s="3">
         <v>185247000</v>
       </c>
-      <c r="AN66" s="3" t="s">
+      <c r="AO66" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6955,8 +7115,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7071,8 +7232,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7187,8 +7351,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7303,8 +7470,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7419,44 +7589,47 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>51686000</v>
+      </c>
+      <c r="E72" s="3">
         <v>50128000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>47641000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>46577000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>43543000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>42215000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>39269000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>38823000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>34435000</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N72" s="3">
         <v>39269000</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>8</v>
       </c>
@@ -7493,50 +7666,53 @@
       <c r="Z72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AA72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB72" s="3">
         <v>83915000</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC72" s="3">
+      <c r="AC72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD72" s="3">
         <v>77751000</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE72" s="3">
+      <c r="AE72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF72" s="3">
         <v>73830000</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG72" s="3">
+      <c r="AG72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH72" s="3">
         <v>73613000</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI72" s="3">
+      <c r="AI72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ72" s="3">
         <v>75874000</v>
       </c>
-      <c r="AJ72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK72" s="3">
+      <c r="AK72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL72" s="3">
         <v>74173000</v>
       </c>
-      <c r="AL72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM72" s="3">
+      <c r="AM72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN72" s="3">
         <v>150754000</v>
       </c>
-      <c r="AN72" s="3" t="s">
+      <c r="AO72" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7651,8 +7827,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7767,8 +7946,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7883,47 +8065,50 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>93500000</v>
+      </c>
+      <c r="E76" s="3">
         <v>87287000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>80671000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>78237000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>78517000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>81848000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>77460000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>73398000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>71550000</v>
-      </c>
-      <c r="L76" s="3">
-        <v>77460000</v>
       </c>
       <c r="M76" s="3">
         <v>77460000</v>
       </c>
       <c r="N76" s="3">
+        <v>77460000</v>
+      </c>
+      <c r="O76" s="3">
         <v>73398000</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>8</v>
       </c>
@@ -7957,50 +8142,53 @@
       <c r="Z76" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AA76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB76" s="3">
         <v>75722000</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC76" s="3">
+      <c r="AC76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD76" s="3">
         <v>70233000</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE76" s="3">
+      <c r="AE76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF76" s="3">
         <v>64485000</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG76" s="3">
+      <c r="AG76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH76" s="3">
         <v>68510000</v>
       </c>
-      <c r="AH76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI76" s="3">
+      <c r="AI76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ76" s="3">
         <v>72585000</v>
       </c>
-      <c r="AJ76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK76" s="3">
+      <c r="AK76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL76" s="3">
         <v>72714000</v>
       </c>
-      <c r="AL76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM76" s="3">
+      <c r="AM76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN76" s="3">
         <v>71339000</v>
       </c>
-      <c r="AN76" s="3" t="s">
+      <c r="AO76" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8115,245 +8303,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3751000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1959000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1676000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1220000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1473000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1891000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>338000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2843000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1597000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1472000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>338000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1639000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2843000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1433000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1597000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>95000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1961000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>250000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1863000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>595000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2265000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1039000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1897000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2250000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>113000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>3003000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2484000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3571000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>457000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>961000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2954000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1019000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>5088000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>2055000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>2908000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>1405000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>956000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>557000</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8394,8 +8591,9 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8432,41 +8630,41 @@
       <c r="N83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
-      <c r="R83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
-      <c r="T83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U83" s="3">
-        <v>0</v>
-      </c>
-      <c r="V83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W83" s="3">
-        <v>0</v>
-      </c>
-      <c r="X83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z83" s="3" t="s">
-        <v>8</v>
+      <c r="O83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+      <c r="U83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+      <c r="W83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z83" s="3">
+        <v>0</v>
       </c>
       <c r="AA83" s="3" t="s">
         <v>8</v>
@@ -8480,38 +8678,41 @@
       <c r="AD83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE83" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG83" s="3">
+      <c r="AE83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH83" s="3">
         <v>2335000</v>
       </c>
-      <c r="AH83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI83" s="3">
+      <c r="AI83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>2167000</v>
       </c>
-      <c r="AJ83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK83" s="3">
+      <c r="AK83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL83" s="3">
         <v>2109000</v>
       </c>
-      <c r="AL83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM83" s="3">
+      <c r="AM83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN83" s="3">
         <v>1918000</v>
       </c>
-      <c r="AN83" s="3" t="s">
+      <c r="AO83" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8626,8 +8827,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8742,8 +8946,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8858,8 +9065,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8974,8 +9184,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9090,8 +9303,11 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -9128,41 +9344,41 @@
       <c r="N89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
-      <c r="V89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
-      <c r="X89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z89" s="3" t="s">
-        <v>8</v>
+      <c r="O89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V89" s="3">
+        <v>0</v>
+      </c>
+      <c r="W89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z89" s="3">
+        <v>0</v>
       </c>
       <c r="AA89" s="3" t="s">
         <v>8</v>
@@ -9176,38 +9392,41 @@
       <c r="AD89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG89" s="3">
+      <c r="AE89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH89" s="3">
         <v>3425000</v>
       </c>
-      <c r="AH89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI89" s="3">
+      <c r="AI89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ89" s="3">
         <v>11412000</v>
       </c>
-      <c r="AJ89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK89" s="3">
+      <c r="AK89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL89" s="3">
         <v>4018000</v>
       </c>
-      <c r="AL89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM89" s="3">
+      <c r="AM89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN89" s="3">
         <v>7657000</v>
       </c>
-      <c r="AN89" s="3" t="s">
+      <c r="AO89" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9248,8 +9467,9 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9286,41 +9506,41 @@
       <c r="N91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O91" s="3">
+      <c r="O91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P91" s="3">
         <v>-2174000</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-2201000</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-1580000</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
-      <c r="X91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z91" s="3" t="s">
-        <v>8</v>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>0</v>
       </c>
       <c r="AA91" s="3" t="s">
         <v>8</v>
@@ -9334,38 +9554,41 @@
       <c r="AD91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG91" s="3">
+      <c r="AE91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-2127000</v>
       </c>
-      <c r="AH91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI91" s="3">
+      <c r="AI91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-3018000</v>
       </c>
-      <c r="AJ91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK91" s="3">
+      <c r="AK91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL91" s="3">
         <v>-1723000</v>
       </c>
-      <c r="AL91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM91" s="3">
+      <c r="AM91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN91" s="3">
         <v>-3451000</v>
       </c>
-      <c r="AN91" s="3" t="s">
+      <c r="AO91" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9480,8 +9703,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9596,8 +9822,11 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -9634,41 +9863,41 @@
       <c r="N94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-      <c r="V94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-      <c r="X94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z94" s="3" t="s">
-        <v>8</v>
+      <c r="O94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z94" s="3">
+        <v>0</v>
       </c>
       <c r="AA94" s="3" t="s">
         <v>8</v>
@@ -9682,38 +9911,41 @@
       <c r="AD94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG94" s="3">
+      <c r="AE94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-1250000</v>
       </c>
-      <c r="AH94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI94" s="3">
+      <c r="AI94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>1740000</v>
       </c>
-      <c r="AJ94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK94" s="3">
+      <c r="AK94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL94" s="3">
         <v>6114000</v>
       </c>
-      <c r="AL94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM94" s="3">
+      <c r="AM94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN94" s="3">
         <v>-1778000</v>
       </c>
-      <c r="AN94" s="3" t="s">
+      <c r="AO94" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9754,8 +9986,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9792,8 +10025,8 @@
       <c r="N96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -9847,31 +10080,34 @@
         <v>0</v>
       </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-5132000</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-4800000</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-4475000</v>
       </c>
-      <c r="AL96" s="3">
-        <v>0</v>
-      </c>
       <c r="AM96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-4521000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9986,8 +10222,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10102,8 +10341,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10218,8 +10460,11 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -10256,41 +10501,41 @@
       <c r="N100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z100" s="3" t="s">
-        <v>8</v>
+      <c r="O100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z100" s="3">
+        <v>0</v>
       </c>
       <c r="AA100" s="3" t="s">
         <v>8</v>
@@ -10304,38 +10549,41 @@
       <c r="AD100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG100" s="3">
+      <c r="AE100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH100" s="3">
         <v>-4640000</v>
       </c>
-      <c r="AH100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI100" s="3">
+      <c r="AI100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>-10929000</v>
       </c>
-      <c r="AJ100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK100" s="3">
+      <c r="AK100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL100" s="3">
         <v>-10075000</v>
       </c>
-      <c r="AL100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM100" s="3">
+      <c r="AM100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN100" s="3">
         <v>-4216000</v>
       </c>
-      <c r="AN100" s="3" t="s">
+      <c r="AO100" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10372,41 +10620,41 @@
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-      <c r="T101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
-      <c r="V101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
-      <c r="X101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z101" s="3" t="s">
-        <v>8</v>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>0</v>
       </c>
       <c r="AA101" s="3" t="s">
         <v>8</v>
@@ -10420,38 +10668,41 @@
       <c r="AD101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG101" s="3">
+      <c r="AE101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH101" s="3">
         <v>211000</v>
       </c>
-      <c r="AH101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI101" s="3">
+      <c r="AI101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>984000</v>
       </c>
-      <c r="AJ101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK101" s="3">
+      <c r="AK101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL101" s="3">
         <v>-1303000</v>
       </c>
-      <c r="AL101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM101" s="3">
+      <c r="AM101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN101" s="3">
         <v>737000</v>
       </c>
-      <c r="AN101" s="3" t="s">
+      <c r="AO101" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -10488,41 +10739,41 @@
       <c r="N102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
-      <c r="T102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
-      <c r="V102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
-      <c r="X102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z102" s="3" t="s">
-        <v>8</v>
+      <c r="O102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z102" s="3">
+        <v>0</v>
       </c>
       <c r="AA102" s="3" t="s">
         <v>8</v>
@@ -10536,34 +10787,37 @@
       <c r="AD102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG102" s="3">
+      <c r="AE102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH102" s="3">
         <v>-2457000</v>
       </c>
-      <c r="AH102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI102" s="3">
+      <c r="AI102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>3207000</v>
       </c>
-      <c r="AJ102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK102" s="3">
+      <c r="AK102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL102" s="3">
         <v>-1246000</v>
       </c>
-      <c r="AL102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM102" s="3">
+      <c r="AM102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN102" s="3">
         <v>2400000</v>
       </c>
-      <c r="AN102" s="3" t="s">
+      <c r="AO102" s="3" t="s">
         <v>8</v>
       </c>
     </row>
